--- a/DEMOWEBSHOP/TestData/TestData.xlsx
+++ b/DEMOWEBSHOP/TestData/TestData.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23ab486ef27cbce8/Desktop/DWS project/AUTOMATIONPROJECT/DEMOWEBSHOP/src/test/resources/testdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vithy\Desktop\Expleo\AUTOMATIONPROJECT\DEMOWEBSHOP\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F25DC773A252ABDACC1048E1C19E71985ADE58E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7CA7BDE-7DAE-4F19-84C6-BBE16E38738F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FD8955-64BA-41C7-B6D0-EFC5040027D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2388" yWindow="864" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>email</t>
   </si>
@@ -37,6 +38,42 @@
   </si>
   <si>
     <t>haritha</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>ConfirmPassword</t>
+  </si>
+  <si>
+    <t>vithya</t>
+  </si>
+  <si>
+    <t>murugesan</t>
+  </si>
+  <si>
+    <t>john</t>
+  </si>
+  <si>
+    <t>peter</t>
+  </si>
+  <si>
+    <t>john123</t>
+  </si>
+  <si>
+    <t>vithyakm12345@gmail.com</t>
+  </si>
+  <si>
+    <t>johnkm12345@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -81,9 +118,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -393,4 +439,76 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E1C7451-0577-4285-B03E-D12A88D73665}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4">
+        <v>123456</v>
+      </c>
+      <c r="E2" s="4">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{8970ED18-C928-4CB7-89BE-748532DFA050}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{4C63C50E-371C-4EED-BAF2-04FDCD954C51}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DEMOWEBSHOP/TestData/TestData.xlsx
+++ b/DEMOWEBSHOP/TestData/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vithy\Desktop\Expleo\AUTOMATIONPROJECT\DEMOWEBSHOP\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FD8955-64BA-41C7-B6D0-EFC5040027D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6010BF32-394C-4CAA-AAB1-13A8A029CCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,10 +70,10 @@
     <t>john123</t>
   </si>
   <si>
-    <t>vithyakm12345@gmail.com</t>
-  </si>
-  <si>
-    <t>johnkm12345@gmail.com</t>
+    <t>vithyakm123456@gmail.com</t>
+  </si>
+  <si>
+    <t>johnkm123456@gmail.com</t>
   </si>
 </sst>
 </file>

--- a/DEMOWEBSHOP/TestData/TestData.xlsx
+++ b/DEMOWEBSHOP/TestData/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vithy\Desktop\Expleo\AUTOMATIONPROJECT\DEMOWEBSHOP\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6010BF32-394C-4CAA-AAB1-13A8A029CCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5821A7A3-84EC-45E7-A0AF-A581DB3E04C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,10 +70,10 @@
     <t>john123</t>
   </si>
   <si>
-    <t>vithyakm123456@gmail.com</t>
-  </si>
-  <si>
-    <t>johnkm123456@gmail.com</t>
+    <t>vithyakm1234567@gmail.com</t>
+  </si>
+  <si>
+    <t>johnkm1234567@gmail.com</t>
   </si>
 </sst>
 </file>
